--- a/new_thu/database/项目库/zlc/沉积形貌/表面原位补形.xlsx
+++ b/new_thu/database/项目库/zlc/沉积形貌/表面原位补形.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -29,15 +29,17 @@
       <name val="宋体"/>
       <charset val="134"/>
       <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,13 +73,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" borderId="2" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -160,9 +171,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7620000" cy="3810000"/>
@@ -179,6 +190,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -476,15 +490,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3643"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Y/mm</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Z/mm</t>
         </is>
@@ -29628,7 +29642,6 @@
     </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -29638,224 +29651,789 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:M36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>参数名称</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>参数名称</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>参数名称</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KUKA程序名称</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Program_Name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L7_160_10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CCD相机</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>GongYe_CCD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>扫描前移动距离X</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Before_Scanning_Y</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>熔覆时前移动距离X</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Before_Deposition_X</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>59.38</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>点温仪</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dian_Temperature</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>扫描前移动距离Y</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Before_Scanning_Y</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>熔覆时前移动距离Y</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Before_Deposition_Y</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>高速相机</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GaoSu_Camera</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>扫描前移动距离Z</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Before_Scanning_Z</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>熔覆时前移动距离Z</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Before_Deposition_Z</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>激光轮廓仪</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Laser_LunKuo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>扫描前等待时间</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Wait_Before_Scanning</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>光斑电压</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Laser_Spot</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>扫描速度</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Scanning_Speed</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>熔覆前保护气时间</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Protection_Gas_Before_Deposition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Y向扫描移动距离</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Scanning_Y_Distacne</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>熔覆后保护气时间</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Protection_Gas_After_Deposition</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>扫描后移动距离X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>After_Scanning_X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>熔覆速度</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deposition_Speed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>扫描后移动距离Y</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>After_Scanning_Y</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>粉桶选择</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Choose_Powder</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>扫描后移动距离Z</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>After_Scanning_Z</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>粉桶转速</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Powder_Delivery_Speed</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>激光功率</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Laser_Power</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>层总数</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Layer_Sum</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>道次数</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pass_Number</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>道次长度</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pass_Distance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>偏移距离</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offset_Distance </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>熔覆后移动距离X</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>After_Deposition_X</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>熔覆后移动距离Y</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>After_Deposition_Y</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>熔覆后移动距离Z</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>After_Deposition_Z</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>层间停留时间</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wait_ between_Layers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>平均道次宽度(mm)</t>
         </is>
       </c>
-      <c r="B1" t="n">
+      <c r="B26" t="n">
         <v>3.21</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>平均熔覆层厚(mm)</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B27" t="n">
         <v>1.58</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>层数</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Y坐标</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>道数</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>X_min</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Y_min</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>X_max</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Y_max</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="30">
+      <c r="A30" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B30" t="n">
         <v>0.79</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C30" t="n">
         <v>15</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D30" t="n">
         <v>56.18</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E30" t="n">
         <v>0.79</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F30" t="n">
         <v>101.12</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G30" t="n">
         <v>0.79</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="31">
+      <c r="A31" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B31" t="n">
         <v>2.37</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C31" t="n">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D31" t="n">
         <v>40.12</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E31" t="n">
         <v>2.37</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F31" t="n">
         <v>117.16</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G31" t="n">
         <v>2.37</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="32">
+      <c r="A32" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B32" t="n">
         <v>3.95</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D32" t="n">
         <v>30.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E32" t="n">
         <v>3.95</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F32" t="n">
         <v>126.8</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G32" t="n">
         <v>3.95</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="33">
+      <c r="A33" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B33" t="n">
         <v>5.53</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C33" t="n">
         <v>37</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D33" t="n">
         <v>20.86</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E33" t="n">
         <v>5.53</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F33" t="n">
         <v>136.42</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G33" t="n">
         <v>5.53</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="34">
+      <c r="A34" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B34" t="n">
         <v>7.11</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C34" t="n">
         <v>42</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D34" t="n">
         <v>14.44</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E34" t="n">
         <v>7.11</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F34" t="n">
         <v>146.05</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G34" t="n">
         <v>7.11</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="35">
+      <c r="A35" t="n">
         <v>6</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B35" t="n">
         <v>8.69</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C35" t="n">
         <v>46</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D35" t="n">
         <v>8.02</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E35" t="n">
         <v>8.69</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F35" t="n">
         <v>152.48</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G35" t="n">
         <v>8.69</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="36">
+      <c r="A36" t="n">
         <v>7</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B36" t="n">
         <v>10.27</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C36" t="n">
         <v>49</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D36" t="n">
         <v>1.6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E36" t="n">
         <v>10.27</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F36" t="n">
         <v>155.68</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G36" t="n">
         <v>10.27</v>
       </c>
     </row>

--- a/new_thu/database/项目库/zlc/沉积形貌/表面原位补形.xlsx
+++ b/new_thu/database/项目库/zlc/沉积形貌/表面原位补形.xlsx
@@ -28,15 +28,15 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -85,7 +85,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf applyAlignment="1" borderId="2" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -29652,7 +29652,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:M36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
